--- a/Result/scale_up_price_model_mjsp.xlsx
+++ b/Result/scale_up_price_model_mjsp.xlsx
@@ -467,7 +467,7 @@
         <v>0.0486490000024665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04565544414098054</v>
+        <v>0.04141793409303544</v>
       </c>
     </row>
     <row r="3">
@@ -484,7 +484,7 @@
         <v>0.0486490000002637</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1141386112767893</v>
+        <v>0.1035448360711341</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>0.04864899999956315</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2282772225535785</v>
+        <v>0.2070896721422681</v>
       </c>
     </row>
     <row r="5">
@@ -518,7 +518,7 @@
         <v>0.04864899999932714</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3424159213330639</v>
+        <v>0.3106345875945356</v>
       </c>
     </row>
     <row r="6">
@@ -535,7 +535,7 @@
         <v>0.05268000000052846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4565544463605614</v>
+        <v>0.4141793454216058</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         <v>0.1064199999999489</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9131091235399762</v>
+        <v>0.8283589002386134</v>
       </c>
     </row>
     <row r="8">
@@ -569,7 +569,7 @@
         <v>0.2359999999999517</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36966333905928</v>
+        <v>1.242538036244492</v>
       </c>
     </row>
   </sheetData>
@@ -622,7 +622,7 @@
         <v>1.638403452772569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04565544414098054</v>
+        <v>0.04141793409303544</v>
       </c>
     </row>
     <row r="3">
@@ -639,7 +639,7 @@
         <v>1.258051347814137</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1141386112767893</v>
+        <v>0.1035448360711341</v>
       </c>
     </row>
     <row r="4">
@@ -656,7 +656,7 @@
         <v>1.014904093554843</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2282772225535785</v>
+        <v>0.2070896721422681</v>
       </c>
     </row>
     <row r="5">
@@ -673,7 +673,7 @@
         <v>0.8841829024748166</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3424159213330639</v>
+        <v>0.3106345875945356</v>
       </c>
     </row>
     <row r="6">
@@ -690,7 +690,7 @@
         <v>0.8357325721046613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4565544463605614</v>
+        <v>0.4141793454216058</v>
       </c>
     </row>
     <row r="7">
@@ -707,7 +707,7 @@
         <v>1.501757132091748</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9131091235399762</v>
+        <v>0.8283589002386134</v>
       </c>
     </row>
     <row r="8">
@@ -724,7 +724,7 @@
         <v>3.25925215005971</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36966333905928</v>
+        <v>1.242538036244492</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +777,7 @@
         <v>3.482533710135268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04565544414098054</v>
+        <v>0.04141793409303544</v>
       </c>
     </row>
     <row r="3">
@@ -794,7 +794,7 @@
         <v>3.049439883594382</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1141386112767893</v>
+        <v>0.1035448360711341</v>
       </c>
     </row>
     <row r="4">
@@ -811,7 +811,7 @@
         <v>2.789048623961491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2282772225535785</v>
+        <v>0.2070896721422681</v>
       </c>
     </row>
     <row r="5">
@@ -828,7 +828,7 @@
         <v>2.648678143591995</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3424159213330639</v>
+        <v>0.3106345875945356</v>
       </c>
     </row>
     <row r="6">
@@ -845,7 +845,7 @@
         <v>2.587133456982873</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4565544463605614</v>
+        <v>0.4141793454216058</v>
       </c>
     </row>
     <row r="7">
@@ -862,7 +862,7 @@
         <v>3.231436219552518</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9131091235399762</v>
+        <v>0.8283589002386134</v>
       </c>
     </row>
     <row r="8">
@@ -879,7 +879,7 @@
         <v>4.984244399888278</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36966333905928</v>
+        <v>1.242538036244492</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +932,7 @@
         <v>2.206999917290672</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04565544414098054</v>
+        <v>0.04141793409303544</v>
       </c>
     </row>
     <row r="3">
@@ -949,7 +949,7 @@
         <v>1.784713339938714</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1141386112767893</v>
+        <v>0.1035448360711341</v>
       </c>
     </row>
     <row r="4">
@@ -966,7 +966,7 @@
         <v>1.518629365177035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2282772225535785</v>
+        <v>0.2070896721422681</v>
       </c>
     </row>
     <row r="5">
@@ -983,7 +983,7 @@
         <v>1.377160078662759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3424159213330639</v>
+        <v>0.3106345875945356</v>
       </c>
     </row>
     <row r="6">
@@ -1000,7 +1000,7 @@
         <v>1.322075056390144</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4565544463605614</v>
+        <v>0.4141793454216058</v>
       </c>
     </row>
     <row r="7">
@@ -1017,7 +1017,7 @@
         <v>1.974925615629848</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9131091235399762</v>
+        <v>0.8283589002386134</v>
       </c>
     </row>
     <row r="8">
@@ -1034,7 +1034,7 @@
         <v>3.72624794072279</v>
       </c>
       <c r="E8" t="n">
-        <v>1.36966333905928</v>
+        <v>1.242538036244492</v>
       </c>
     </row>
   </sheetData>
